--- a/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F33" t="n">
         <v>63</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         <v>138</v>
       </c>
       <c r="F42" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
         <v>144</v>
@@ -3189,7 +3189,7 @@
         <v>463</v>
       </c>
       <c r="F45" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
         <v>471</v>
@@ -4553,7 +4553,7 @@
         <v>208</v>
       </c>
       <c r="F67" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
         <v>229</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F76" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L76" t="n">
         <v>29</v>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F84" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>104</v>
       </c>
       <c r="F104" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
         <v>104</v>
@@ -6909,7 +6909,7 @@
         <v>266</v>
       </c>
       <c r="F105" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
         <v>266</v>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F115" t="n">
         <v>47</v>
@@ -7541,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L115" t="n">
         <v>5</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F116" t="n">
         <v>89</v>
@@ -7603,10 +7603,10 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K116" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F186" t="n">
         <v>28</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K186" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F12" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L12" t="n">
         <v>11</v>
@@ -1406,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
         <v>233</v>
@@ -1527,13 +1527,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -3018,10 +3018,10 @@
         <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>30</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>30</v>
@@ -4367,7 +4367,7 @@
         <v>219</v>
       </c>
       <c r="F64" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K64" t="n">
         <v>222</v>
@@ -4553,7 +4553,7 @@
         <v>208</v>
       </c>
       <c r="F67" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
         <v>229</v>
@@ -4677,7 +4677,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
         <v>5</v>
@@ -5111,7 +5111,7 @@
         <v>169</v>
       </c>
       <c r="F76" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K76" t="n">
         <v>198</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F111" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
         <v>7</v>
       </c>
       <c r="K111" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L111" t="n">
         <v>9</v>
@@ -7467,7 +7467,7 @@
         <v>125</v>
       </c>
       <c r="F114" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
         <v>125</v>
@@ -7591,7 +7591,7 @@
         <v>92</v>
       </c>
       <c r="F116" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
         <v>93</v>
@@ -7653,7 +7653,7 @@
         <v>23</v>
       </c>
       <c r="F117" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -7665,13 +7665,13 @@
         <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K117" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -11125,7 +11125,7 @@
         <v>6</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K173" t="n">
         <v>7</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F186" t="n">
         <v>28</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K186" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F11" t="n">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F12" t="n">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F18" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -1639,7 +1639,7 @@
         <v>140</v>
       </c>
       <c r="F20" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>142</v>
@@ -1825,7 +1825,7 @@
         <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>55</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" t="n">
         <v>150</v>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F34" t="n">
         <v>231</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F39" t="n">
         <v>30</v>
@@ -2829,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
+        <v>13</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
         <v>15</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>18</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F42" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3018,13 +3018,13 @@
         <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F43" t="n">
         <v>133</v>
@@ -3077,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F45" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3201,10 +3201,10 @@
         <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="L45" t="n">
         <v>8</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
         <v>44</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F64" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K64" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F65" t="n">
         <v>31</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F67" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L67" t="n">
         <v>21</v>
@@ -4615,7 +4615,7 @@
         <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4627,13 +4627,13 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F76" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,13 +5123,13 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K76" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L76" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L82" t="n">
         <v>2</v>
@@ -5607,7 +5607,7 @@
         <v>221</v>
       </c>
       <c r="F84" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
         <v>221</v>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -6363,10 +6363,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F104" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6862,13 +6862,13 @@
         <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F105" t="n">
         <v>258</v>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -7048,10 +7048,10 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>5</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7107,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K108" t="n">
         <v>5</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7293,13 +7293,13 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K111" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F112" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K112" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
         <v>15</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F114" t="n">
         <v>124</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F115" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -7541,13 +7541,13 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -7588,25 +7588,25 @@
         </is>
       </c>
       <c r="E116" t="n">
+        <v>91</v>
+      </c>
+      <c r="F116" t="n">
+        <v>91</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
         <v>92</v>
-      </c>
-      <c r="F116" t="n">
-        <v>92</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>93</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>4</v>
       </c>
       <c r="K117" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F118" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -7724,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F122" t="n">
         <v>34</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -8096,13 +8096,13 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8226,10 +8226,10 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F127" t="n">
         <v>96</v>
@@ -8285,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F128" t="n">
         <v>170</v>
@@ -8347,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F129" t="n">
         <v>30</v>
@@ -8409,10 +8409,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L129" t="n">
         <v>1</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F134" t="n">
         <v>70</v>
@@ -8716,13 +8716,13 @@
         <v>60</v>
       </c>
       <c r="I134" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
         <v>1</v>
       </c>
       <c r="K134" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="L134" t="n">
         <v>7</v>
@@ -9203,7 +9203,7 @@
         <v>41</v>
       </c>
       <c r="F142" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -9215,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>41</v>
@@ -9885,10 +9885,10 @@
         <v>94</v>
       </c>
       <c r="F153" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G153" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>66</v>
@@ -10892,10 +10892,10 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M169" t="n">
         <v>1</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F170" t="n">
         <v>2</v>
@@ -10951,13 +10951,13 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K170" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L170" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -11137,10 +11137,10 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" t="n">
         <v>4</v>
-      </c>
-      <c r="K173" t="n">
-        <v>7</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F186" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -11946,7 +11946,7 @@
         <v>4</v>
       </c>
       <c r="K186" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>64</v>
       </c>
       <c r="F191" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191" t="n">
         <v>64</v>

--- a/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F12" t="n">
         <v>509</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
@@ -2569,7 +2569,7 @@
         <v>133</v>
       </c>
       <c r="F35" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>133</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F42" t="n">
         <v>123</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -4367,7 +4367,7 @@
         <v>209</v>
       </c>
       <c r="F64" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
         <v>212</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F67" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L67" t="n">
         <v>21</v>
@@ -4677,19 +4677,19 @@
         <v>5</v>
       </c>
       <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
         <v>3</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2</v>
       </c>
       <c r="K69" t="n">
         <v>5</v>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>172</v>
       </c>
       <c r="F76" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
         <v>199</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -6351,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>2</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F112" t="n">
         <v>187</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K112" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>51</v>
       </c>
       <c r="F115" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K115" t="n">
         <v>57</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
         <v>40</v>
@@ -9215,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -10443,19 +10443,19 @@
         <v>1</v>
       </c>
       <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
         <v>1</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" t="n">
-        <v>0</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
